--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-r.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-r.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5645" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5645" uniqueCount="669">
   <si>
     <t>Property</t>
   </si>
@@ -866,7 +866,7 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
+    <t xml:space="preserve">pattern:code}
 </t>
   </si>
   <si>
@@ -1755,6 +1755,13 @@
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;code value="component:&amp;lt;slice&amp;gt;.code"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>containment by OBX-4?</t>
   </si>
   <si>
@@ -1873,6 +1880,10 @@
   </si>
   <si>
     <t>Observation.component.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
   </si>
   <si>
     <t>Observation.component:predicted.code.coding:sct</t>
@@ -12035,7 +12046,7 @@
         <v>81</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>81</v>
+        <v>555</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>81</v>
@@ -12093,7 +12104,7 @@
         <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>81</v>
@@ -12104,10 +12115,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12219,10 +12230,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12336,10 +12347,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12455,10 +12466,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12484,13 +12495,13 @@
         <v>232</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O86" t="s" s="2">
         <v>261</v>
@@ -12542,7 +12553,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>91</v>
@@ -12560,7 +12571,7 @@
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>266</v>
@@ -12574,10 +12585,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12600,16 +12611,16 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O87" t="s" s="2">
         <v>387</v>
@@ -12661,7 +12672,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12679,7 +12690,7 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>390</v>
@@ -12693,10 +12704,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12722,13 +12733,13 @@
         <v>232</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O88" t="s" s="2">
         <v>435</v>
@@ -12780,7 +12791,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12812,10 +12823,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12841,10 +12852,10 @@
         <v>232</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>444</v>
@@ -12899,7 +12910,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12931,10 +12942,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12960,10 +12971,10 @@
         <v>82</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>495</v>
@@ -13018,7 +13029,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13050,13 +13061,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>550</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>81</v>
@@ -13081,10 +13092,10 @@
         <v>492</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>553</v>
@@ -13160,7 +13171,7 @@
         <v>81</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
@@ -13171,10 +13182,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13286,10 +13297,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13403,10 +13414,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13522,10 +13533,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13551,13 +13562,13 @@
         <v>232</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O95" t="s" s="2">
         <v>261</v>
@@ -13609,7 +13620,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>91</v>
@@ -13627,7 +13638,7 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>266</v>
@@ -13641,10 +13652,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13756,10 +13767,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13873,10 +13884,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13948,7 +13959,7 @@
         <v>81</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>272</v>
+        <v>595</v>
       </c>
       <c r="AC98" s="2"/>
       <c r="AD98" t="s" s="2">
@@ -13990,10 +14001,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="C99" t="s" s="2">
         <v>274</v>
@@ -14040,7 +14051,7 @@
         <v>81</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>81</v>
@@ -14109,10 +14120,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C100" t="s" s="2">
         <v>322</v>
@@ -14159,7 +14170,7 @@
         <v>81</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>81</v>
@@ -14178,7 +14189,7 @@
       </c>
       <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>81</v>
@@ -14228,10 +14239,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14347,10 +14358,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14373,16 +14384,16 @@
         <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>387</v>
@@ -14422,7 +14433,7 @@
         <v>81</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AC102" s="2"/>
       <c r="AD102" t="s" s="2">
@@ -14432,7 +14443,7 @@
         <v>117</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14450,7 +14461,7 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>390</v>
@@ -14464,13 +14475,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>81</v>
@@ -14495,13 +14506,13 @@
         <v>383</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O103" t="s" s="2">
         <v>387</v>
@@ -14553,7 +14564,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14571,7 +14582,7 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>390</v>
@@ -14585,10 +14596,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14700,10 +14711,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14817,10 +14828,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14936,10 +14947,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15055,10 +15066,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15172,10 +15183,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15289,10 +15300,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15408,10 +15419,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15437,13 +15448,13 @@
         <v>232</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O111" t="s" s="2">
         <v>435</v>
@@ -15495,7 +15506,7 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15527,10 +15538,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15556,10 +15567,10 @@
         <v>232</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>444</v>
@@ -15614,7 +15625,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15646,10 +15657,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15675,10 +15686,10 @@
         <v>82</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>495</v>
@@ -15733,7 +15744,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15765,13 +15776,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>550</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>81</v>
@@ -15796,10 +15807,10 @@
         <v>492</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>553</v>
@@ -15875,7 +15886,7 @@
         <v>81</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>81</v>
@@ -15886,10 +15897,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16001,10 +16012,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16118,10 +16129,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16237,10 +16248,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16266,13 +16277,13 @@
         <v>232</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O118" t="s" s="2">
         <v>261</v>
@@ -16324,7 +16335,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>91</v>
@@ -16342,7 +16353,7 @@
         <v>81</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>266</v>
@@ -16356,10 +16367,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16471,10 +16482,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16588,10 +16599,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16663,7 +16674,7 @@
         <v>81</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>272</v>
+        <v>595</v>
       </c>
       <c r="AC121" s="2"/>
       <c r="AD121" t="s" s="2">
@@ -16705,10 +16716,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C122" t="s" s="2">
         <v>274</v>
@@ -16755,7 +16766,7 @@
         <v>81</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>81</v>
@@ -16824,10 +16835,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>322</v>
@@ -16943,10 +16954,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17062,10 +17073,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17088,16 +17099,16 @@
         <v>92</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O125" t="s" s="2">
         <v>387</v>
@@ -17137,7 +17148,7 @@
         <v>81</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AC125" s="2"/>
       <c r="AD125" t="s" s="2">
@@ -17147,7 +17158,7 @@
         <v>117</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17165,7 +17176,7 @@
         <v>81</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>390</v>
@@ -17179,13 +17190,13 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>81</v>
@@ -17210,13 +17221,13 @@
         <v>383</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O126" t="s" s="2">
         <v>387</v>
@@ -17268,7 +17279,7 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17286,7 +17297,7 @@
         <v>81</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>390</v>
@@ -17300,10 +17311,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17415,10 +17426,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17532,10 +17543,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17651,10 +17662,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17770,10 +17781,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17816,7 +17827,7 @@
         <v>81</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>81</v>
@@ -17887,10 +17898,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18004,10 +18015,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18052,7 +18063,7 @@
         <v>81</v>
       </c>
       <c r="S133" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="T133" t="s" s="2">
         <v>81</v>
@@ -18123,10 +18134,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18152,13 +18163,13 @@
         <v>232</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O134" t="s" s="2">
         <v>435</v>
@@ -18210,7 +18221,7 @@
         <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18242,10 +18253,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18271,10 +18282,10 @@
         <v>232</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>444</v>
@@ -18329,7 +18340,7 @@
         <v>81</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18361,10 +18372,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18390,10 +18401,10 @@
         <v>82</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N136" t="s" s="2">
         <v>495</v>
@@ -18448,7 +18459,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18480,13 +18491,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>550</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>81</v>
@@ -18511,10 +18522,10 @@
         <v>492</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="N137" t="s" s="2">
         <v>553</v>
@@ -18590,7 +18601,7 @@
         <v>81</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>81</v>
@@ -18601,10 +18612,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18716,10 +18727,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18833,10 +18844,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18952,10 +18963,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18981,13 +18992,13 @@
         <v>232</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O141" t="s" s="2">
         <v>261</v>
@@ -19039,7 +19050,7 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>91</v>
@@ -19057,7 +19068,7 @@
         <v>81</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>266</v>
@@ -19071,10 +19082,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19186,10 +19197,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19303,10 +19314,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19378,7 +19389,7 @@
         <v>81</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>272</v>
+        <v>595</v>
       </c>
       <c r="AC144" s="2"/>
       <c r="AD144" t="s" s="2">
@@ -19420,10 +19431,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C145" t="s" s="2">
         <v>274</v>
@@ -19470,7 +19481,7 @@
         <v>81</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>81</v>
@@ -19539,10 +19550,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19658,10 +19669,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19684,16 +19695,16 @@
         <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O147" t="s" s="2">
         <v>387</v>
@@ -19745,7 +19756,7 @@
         <v>81</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -19763,7 +19774,7 @@
         <v>81</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>390</v>
@@ -19777,10 +19788,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19806,13 +19817,13 @@
         <v>232</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O148" t="s" s="2">
         <v>435</v>
@@ -19864,7 +19875,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -19896,10 +19907,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19925,10 +19936,10 @@
         <v>232</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N149" t="s" s="2">
         <v>444</v>
@@ -19983,7 +19994,7 @@
         <v>81</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20015,10 +20026,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20044,10 +20055,10 @@
         <v>82</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N150" t="s" s="2">
         <v>495</v>
@@ -20102,7 +20113,7 @@
         <v>81</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
